--- a/files/九龙-油麻地-原舍.xlsx
+++ b/files/九龙-油麻地-原舍.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原舍 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4761,957 +4625,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>原舍 - 原舍 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>84 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>17 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>54 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>27&amp;28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 674呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 572呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$546万
-$19,077/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$538万
-$18,811/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-$582万
-$19,155/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$536万
-$18,738/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-$575万
-$18,069/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-$469万
-$21,518/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-$534万
-$17,566/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-$573万
-$18,852/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$477万
-$16,689/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-$563万
-$17,714/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-$460万
-$21,092/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-$571万
-$18,776/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$476万
-$16,626/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-$606万
-$19,060/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-$455万
-$20,885/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-$523万
-$17,207/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-$600万
-$18,871/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-$415万
-$19,028/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-$513万
-$16,865/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-$547万
-$17,192/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-$411万
-$18,835/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-$560万
-$18,438/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-$594万
-$18,686/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-$446万
-$20,472/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-$558万
-$18,365/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$497万
-$17,385/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-$541万
-$17,022/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-$407万
-$18,651/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-$556万
-$18,293/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-$378万
-$17,339/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 218呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 267呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 180呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-油麻地-原舍.xlsx
+++ b/files/九龙-油麻地-原舍.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原舍" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4625,4 +4804,957 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>原舍 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 674呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 572呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$546万
+$19,077/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$538万
+$18,811/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+$582万
+$19,155/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$536万
+$18,738/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+$575万
+$18,069/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+$469万
+$21,518/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+$534万
+$17,566/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+$573万
+$18,852/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$477万
+$16,689/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+$563万
+$17,714/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+$460万
+$21,092/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+$571万
+$18,776/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$476万
+$16,626/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+$606万
+$19,060/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+$455万
+$20,885/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+$523万
+$17,207/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+$600万
+$18,871/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+$415万
+$19,028/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+$513万
+$16,865/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+$547万
+$17,192/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+$411万
+$18,835/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+$560万
+$18,438/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+$594万
+$18,686/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+$446万
+$20,472/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+$558万
+$18,365/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$497万
+$17,385/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+$541万
+$17,022/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+$407万
+$18,651/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+$556万
+$18,293/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+$378万
+$17,339/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 218呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 267呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 180呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-油麻地-原舍.xlsx
+++ b/files/九龙-油麻地-原舍.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4923,52 +4923,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 674呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>C | 572呎 (2房)
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 674呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 572呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -4976,7 +4976,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -4984,7 +4984,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -4992,7 +4992,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5000,7 +5000,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5015,7 +5015,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5023,7 +5023,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5031,7 +5031,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5039,7 +5039,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5054,7 +5054,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5062,7 +5062,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5070,7 +5070,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5078,7 +5078,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5093,7 +5093,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5101,7 +5101,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5109,7 +5109,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5117,7 +5117,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5132,7 +5132,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5140,7 +5140,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5148,7 +5148,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5156,7 +5156,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5171,7 +5171,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5179,7 +5179,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5187,7 +5187,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5195,7 +5195,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5210,7 +5210,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5218,7 +5218,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5226,7 +5226,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5234,7 +5234,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5249,7 +5249,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5265,7 +5265,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5273,7 +5273,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5288,7 +5288,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5304,7 +5304,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5312,7 +5312,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5374,7 +5374,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5382,7 +5382,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5390,7 +5390,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5491,7 +5491,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5530,7 +5530,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5569,7 +5569,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5647,7 +5647,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5655,7 +5655,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5678,7 +5678,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5686,7 +5686,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5694,7 +5694,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5702,7 +5702,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5717,7 +5717,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -5725,7 +5725,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -5733,7 +5733,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -5741,7 +5741,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/files/九龙-油麻地-原舍.xlsx
+++ b/files/九龙-油麻地-原舍.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -763,6 +787,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -813,6 +857,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -863,6 +927,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -913,6 +997,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -963,6 +1067,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1013,6 +1137,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1063,6 +1207,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1113,6 +1277,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1163,6 +1347,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1213,6 +1417,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1263,6 +1487,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1313,6 +1557,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1363,6 +1627,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1413,6 +1697,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1463,6 +1767,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1513,6 +1837,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1563,6 +1907,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1613,6 +1977,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1663,6 +2047,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1713,6 +2117,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1763,6 +2187,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1813,6 +2257,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1863,6 +2327,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1913,6 +2397,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1963,6 +2467,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2013,6 +2537,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2063,6 +2607,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2113,6 +2677,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2163,6 +2747,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2213,6 +2817,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2263,6 +2887,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2313,6 +2957,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2363,6 +3027,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2413,6 +3097,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2459,6 +3163,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>5019520</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>17551</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2509,6 +3229,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2559,6 +3299,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2609,6 +3369,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2655,6 +3435,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>4949600</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>17306</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2705,6 +3501,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2751,6 +3567,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>4315720</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>19797</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2797,6 +3629,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>5746000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>18069</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2843,6 +3691,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>4930280</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>17239</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2889,6 +3753,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>5357160</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>17622</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2939,6 +3819,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2989,6 +3889,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3039,6 +3959,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3085,6 +4025,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>5340000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>17566</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3131,6 +4087,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>4230160</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>19404</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3177,6 +4149,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>5633000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>17714</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3223,6 +4211,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>4773000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>16689</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3269,6 +4273,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>5272520</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>17344</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3315,6 +4335,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>4188760</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>19214</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3361,6 +4397,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>5576120</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>17535</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3407,6 +4459,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>4755000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>16626</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3453,6 +4521,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>5251360</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>17274</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3499,6 +4583,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>4148000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>19028</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3545,6 +4645,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>5520920</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>17361</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3595,6 +4711,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3641,6 +4777,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>5231000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>17207</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3687,6 +4839,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>4106000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>18835</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3733,6 +4901,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>5467000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>17192</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3783,6 +4967,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3829,6 +5033,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>5127000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>16865</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3875,6 +5095,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>4105960</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>18835</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3921,6 +5157,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>5466640</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>17191</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3971,6 +5223,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4017,6 +5289,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>5156600</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>16962</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4063,6 +5351,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>4066000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>18651</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4109,6 +5413,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>5413000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>17022</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4139,21 +5459,37 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>4972000</v>
+        <v>4575000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>17385</v>
+        <v>15997</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>4575000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>15997</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -4201,6 +5537,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>5136360</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>16896</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4247,6 +5599,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>3780000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>17339</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4297,6 +5665,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4347,6 +5735,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4393,6 +5801,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>5116120</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>16829</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>尊盈投資計劃</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4443,6 +5867,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4493,6 +5937,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4543,6 +6007,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4593,6 +6077,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4643,6 +6147,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4693,6 +6217,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4743,6 +6287,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4793,13 +6357,33 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4869,7 +6453,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4879,7 +6463,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4923,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 674呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 572呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 674呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 572呎 (2房)
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -4976,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -4984,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -4992,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5000,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5015,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5023,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5031,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5039,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5054,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5062,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5070,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5078,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5093,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5101,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5109,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5117,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5132,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5140,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5148,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5156,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5171,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5179,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5187,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5195,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5210,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5218,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5226,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5234,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5249,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5265,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5273,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5288,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5304,7 +6888,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5312,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5348,7 +6932,7 @@
           <t>C | 318呎 (1房)
 $575万
 $18,069/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -5371,10 +6955,10 @@
           <t>A | 304呎 (1房)
 $534万
 $17,566/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5382,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5390,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5418,7 +7002,7 @@
           <t>B | 286呎 (1房)
 $477万
 $16,689/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -5426,7 +7010,7 @@
           <t>C | 318呎 (1房)
 $563万
 $17,714/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -5457,7 +7041,7 @@
           <t>B | 286呎 (1房)
 $476万
 $16,626/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5488,10 +7072,10 @@
           <t>A | 304呎 (1房)
 $523万
 $17,207/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5512,7 +7096,7 @@
           <t>D | 218呎 (开放式)
 $415万
 $19,028/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -5527,10 +7111,10 @@
           <t>A | 304呎 (1房)
 $513万
 $16,865/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5543,7 +7127,7 @@
           <t>C | 318呎 (1房)
 $547万
 $17,192/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -5551,7 +7135,7 @@
           <t>D | 218呎 (开放式)
 $411万
 $18,835/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -5569,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5608,12 +7192,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
-$497万
-$17,385/呎
-(在售)</t>
+$458万
+$15,997/呎
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -5621,7 +7205,7 @@
           <t>C | 318呎 (1房)
 $541万
 $17,022/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -5629,7 +7213,7 @@
           <t>D | 218呎 (开放式)
 $407万
 $18,651/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -5647,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5655,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5668,7 +7252,7 @@
           <t>D | 218呎 (开放式)
 $378万
 $17,339/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -5678,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -5686,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -5694,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -5702,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -5717,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -5725,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -5733,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -5741,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/files/九龙-油麻地-原舍.xlsx
+++ b/files/九龙-油麻地-原舍.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6507,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 674呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>C | 572呎 (2房)
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 674呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 572呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6568,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6576,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6584,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6599,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6607,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6615,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6623,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6638,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6646,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6654,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6662,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6677,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6685,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6693,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6701,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6716,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6724,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6732,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6740,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6755,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6763,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6771,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6779,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6794,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6802,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6810,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6818,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6833,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6849,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6857,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6872,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6888,7 +6888,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6896,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6958,7 +6958,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6966,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6974,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7075,7 +7075,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7114,7 +7114,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7153,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7231,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7239,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7262,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -7270,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7278,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7286,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7301,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -7309,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -7317,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -7325,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/files/九龙-油麻地-原舍.xlsx
+++ b/files/九龙-油麻地-原舍.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -6507,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 674呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 572呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 674呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 572呎 (2房)
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6568,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6576,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6584,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6599,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6607,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6615,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6623,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6638,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6646,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6654,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6662,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6677,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6685,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6693,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6701,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6716,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6724,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6732,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6740,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6755,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6763,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6771,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6779,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6794,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6802,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6810,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6818,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6833,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6849,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6857,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6872,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6888,7 +6888,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6896,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6958,7 +6958,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6966,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6974,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7010,7 +7010,7 @@
           <t>C | 318呎 (1房)
 $563万
 $17,714/呎
-(26年-06月-26日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -7075,7 +7075,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7096,7 +7096,7 @@
           <t>D | 218呎 (开放式)
 $415万
 $19,028/呎
-(26年-06月-28日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -7111,10 +7111,10 @@
           <t>A | 304呎 (1房)
 $513万
 $16,865/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
+(26年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7127,7 +7127,7 @@
           <t>C | 318呎 (1房)
 $547万
 $17,192/呎
-(26年-06月-26日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -7153,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7205,7 +7205,7 @@
           <t>C | 318呎 (1房)
 $541万
 $17,022/呎
-(26年-06月-26日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -7213,7 +7213,7 @@
           <t>D | 218呎 (开放式)
 $407万
 $18,651/呎
-(26年-06月-26日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7239,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7262,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -7270,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7278,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7286,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7301,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -7309,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -7317,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -7325,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/files/九龙-油麻地-原舍.xlsx
+++ b/files/九龙-油麻地-原舍.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -6507,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 674呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>C | 572呎 (2房)
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 674呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 572呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6568,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6576,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6584,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6599,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6607,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6615,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6623,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6638,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6646,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6654,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6662,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6677,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6685,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6693,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6701,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6716,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6724,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6732,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6740,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6755,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6763,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6771,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6779,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6794,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6802,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6810,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6818,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6833,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6849,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6857,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6872,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6888,7 +6888,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6896,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6932,7 +6932,7 @@
           <t>C | 318呎 (1房)
 $575万
 $18,069/呎
-(26年-06月-26日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -6955,10 +6955,10 @@
           <t>A | 304呎 (1房)
 $534万
 $17,566/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6966,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6974,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7002,7 +7002,7 @@
           <t>B | 286呎 (1房)
 $477万
 $16,689/呎
-(26年-06月-26日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -7010,7 +7010,7 @@
           <t>C | 318呎 (1房)
 $563万
 $17,714/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -7041,7 +7041,7 @@
           <t>B | 286呎 (1房)
 $476万
 $16,626/呎
-(26年-06月-26日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7072,10 +7072,10 @@
           <t>A | 304呎 (1房)
 $523万
 $17,207/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7096,7 +7096,7 @@
           <t>D | 218呎 (开放式)
 $415万
 $19,028/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -7111,10 +7111,10 @@
           <t>A | 304呎 (1房)
 $513万
 $16,865/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7127,7 +7127,7 @@
           <t>C | 318呎 (1房)
 $547万
 $17,192/呎
-(26年-07月-19日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -7135,7 +7135,7 @@
           <t>D | 218呎 (开放式)
 $411万
 $18,835/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7197,7 +7197,7 @@
           <t>B | 286呎 (1房)
 $458万
 $15,997/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -7205,7 +7205,7 @@
           <t>C | 318呎 (1房)
 $541万
 $17,022/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -7213,7 +7213,7 @@
           <t>D | 218呎 (开放式)
 $407万
 $18,651/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7239,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7252,7 +7252,7 @@
           <t>D | 218呎 (开放式)
 $378万
 $17,339/呎
-(26年-06月-26日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -7270,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7278,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7286,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7301,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -7309,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -7317,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -7325,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/files/九龙-油麻地-原舍.xlsx
+++ b/files/九龙-油麻地-原舍.xlsx
@@ -6932,7 +6932,7 @@
           <t>C | 318呎 (1房)
 $575万
 $18,069/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -6955,7 +6955,7 @@
           <t>A | 304呎 (1房)
 $534万
 $17,566/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -7002,7 +7002,7 @@
           <t>B | 286呎 (1房)
 $477万
 $16,689/呎
-(26年-07月)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -7010,7 +7010,7 @@
           <t>C | 318呎 (1房)
 $563万
 $17,714/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -7041,7 +7041,7 @@
           <t>B | 286呎 (1房)
 $476万
 $16,626/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7072,7 +7072,7 @@
           <t>A | 304呎 (1房)
 $523万
 $17,207/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -7096,7 +7096,7 @@
           <t>D | 218呎 (开放式)
 $415万
 $19,028/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
           <t>A | 304呎 (1房)
 $513万
 $16,865/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -7127,7 +7127,7 @@
           <t>C | 318呎 (1房)
 $547万
 $17,192/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -7135,7 +7135,7 @@
           <t>D | 218呎 (开放式)
 $411万
 $18,835/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
           <t>B | 286呎 (1房)
 $458万
 $15,997/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -7205,7 +7205,7 @@
           <t>C | 318呎 (1房)
 $541万
 $17,022/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -7213,7 +7213,7 @@
           <t>D | 218呎 (开放式)
 $407万
 $18,651/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
           <t>D | 218呎 (开放式)
 $378万
 $17,339/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-油麻地-原舍.xlsx
+++ b/files/九龙-油麻地-原舍.xlsx
@@ -3618,7 +3618,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -6932,7 +6932,7 @@
           <t>C | 318呎 (1房)
 $575万
 $18,069/呎
-(26年-06月-26日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -7041,7 +7041,7 @@
           <t>B | 286呎 (1房)
 $476万
 $16,626/呎
-(26年-06月-26日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7252,7 +7252,7 @@
           <t>D | 218呎 (开放式)
 $378万
 $17,339/呎
-(26年-06月-26日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
     </row>
